--- a/data/fmsForecastOutput/File1/RPT_RPT5740645592539NW_fmsForecastOutput.xlsx
+++ b/data/fmsForecastOutput/File1/RPT_RPT5740645592539NW_fmsForecastOutput.xlsx
@@ -1878,7 +1878,7 @@
         <v>360.8432324213942</v>
       </c>
       <c r="D8" s="149" t="n">
-        <v>397.5823581854565</v>
+        <v>397.5823581854567</v>
       </c>
       <c r="E8" s="149" t="n">
         <v>436.0703541058004</v>
@@ -1893,7 +1893,7 @@
         <v>37.95734072767167</v>
       </c>
       <c r="I8" s="149" t="n">
-        <v>43.66722404083776</v>
+        <v>43.66722404083777</v>
       </c>
       <c r="J8" s="149" t="n">
         <v>50.05983533348024</v>
@@ -1908,7 +1908,7 @@
         <v>46968978.51875787</v>
       </c>
       <c r="N8" s="152" t="n">
-        <v>54905364.79002392</v>
+        <v>54905364.79002393</v>
       </c>
       <c r="O8" s="152" t="n">
         <v>63853119.24475258</v>
@@ -1928,7 +1928,7 @@
         <v>437.633889510427</v>
       </c>
       <c r="U8" s="149" t="n">
-        <v>482.1914287981891</v>
+        <v>482.1914287981892</v>
       </c>
       <c r="V8" s="149" t="n">
         <v>528.8700134041808</v>
@@ -1943,7 +1943,7 @@
         <v>46.98162310229268</v>
       </c>
       <c r="Z8" s="149" t="n">
-        <v>54.04325572400953</v>
+        <v>54.04325572400955</v>
       </c>
       <c r="AA8" s="149" t="n">
         <v>61.9477854562887</v>
@@ -1958,7 +1958,7 @@
         <v>46968978.51875787</v>
       </c>
       <c r="AE8" s="152" t="n">
-        <v>54905364.79002392</v>
+        <v>54905364.79002393</v>
       </c>
       <c r="AF8" s="152" t="n">
         <v>63853119.24475258</v>
@@ -2025,7 +2025,7 @@
         <v>843.8768162922767</v>
       </c>
       <c r="D9" s="156" t="n">
-        <v>936.5563090164421</v>
+        <v>936.5563090164419</v>
       </c>
       <c r="E9" s="156" t="n">
         <v>1026.822939227442</v>
@@ -2040,13 +2040,13 @@
         <v>59.36287213543368</v>
       </c>
       <c r="I9" s="156" t="n">
-        <v>66.88229688067594</v>
+        <v>66.88229688067592</v>
       </c>
       <c r="J9" s="156" t="n">
-        <v>76.03645831912405</v>
+        <v>76.03645831912408</v>
       </c>
       <c r="K9" s="156" t="n">
-        <v>85.2166152435603</v>
+        <v>85.21661524356033</v>
       </c>
       <c r="L9" s="157" t="n">
         <v>96.89026167872966</v>
@@ -2055,13 +2055,13 @@
         <v>16051068.4221231</v>
       </c>
       <c r="N9" s="159" t="n">
-        <v>18215702.29065886</v>
+        <v>18215702.29065885</v>
       </c>
       <c r="O9" s="159" t="n">
-        <v>20851304.95987435</v>
+        <v>20851304.95987436</v>
       </c>
       <c r="P9" s="159" t="n">
-        <v>23510955.76210328</v>
+        <v>23510955.76210329</v>
       </c>
       <c r="Q9" s="160" t="n">
         <v>26957478.10373155</v>
@@ -2075,7 +2075,7 @@
         <v>855.9568829780011</v>
       </c>
       <c r="U9" s="156" t="n">
-        <v>949.9630793523818</v>
+        <v>949.9630793523817</v>
       </c>
       <c r="V9" s="156" t="n">
         <v>1041.521873172326</v>
@@ -2090,13 +2090,13 @@
         <v>59.61199779486421</v>
       </c>
       <c r="Z9" s="156" t="n">
-        <v>67.16374838471222</v>
+        <v>67.16374838471221</v>
       </c>
       <c r="AA9" s="156" t="n">
-        <v>76.35859284669799</v>
+        <v>76.35859284669802</v>
       </c>
       <c r="AB9" s="156" t="n">
-        <v>85.58194745224543</v>
+        <v>85.58194745224546</v>
       </c>
       <c r="AC9" s="157" t="n">
         <v>97.31166476773402</v>
@@ -2105,13 +2105,13 @@
         <v>16051068.4221231</v>
       </c>
       <c r="AE9" s="159" t="n">
-        <v>18215702.29065886</v>
+        <v>18215702.29065885</v>
       </c>
       <c r="AF9" s="159" t="n">
-        <v>20851304.95987435</v>
+        <v>20851304.95987436</v>
       </c>
       <c r="AG9" s="159" t="n">
-        <v>23510955.76210328</v>
+        <v>23510955.76210329</v>
       </c>
       <c r="AH9" s="160" t="n">
         <v>26957478.10373155</v>
@@ -2173,7 +2173,7 @@
         <v>422.42847897414</v>
       </c>
       <c r="D10" s="162" t="n">
-        <v>464.1200286038718</v>
+        <v>464.1200286038719</v>
       </c>
       <c r="E10" s="162" t="n">
         <v>508.0179470973285</v>
@@ -2188,7 +2188,7 @@
         <v>41.79591715781295</v>
       </c>
       <c r="I10" s="162" t="n">
-        <v>47.80050320800892</v>
+        <v>47.80050320800893</v>
       </c>
       <c r="J10" s="162" t="n">
         <v>54.65634921982944</v>
@@ -2203,7 +2203,7 @@
         <v>63020046.94088096</v>
       </c>
       <c r="N10" s="165" t="n">
-        <v>73121067.08068278</v>
+        <v>73121067.0806828</v>
       </c>
       <c r="O10" s="165" t="n">
         <v>84704424.20462692</v>
@@ -2223,7 +2223,7 @@
         <v>499.8535852818945</v>
       </c>
       <c r="U10" s="162" t="n">
-        <v>549.6110000772059</v>
+        <v>549.611000077206</v>
       </c>
       <c r="V10" s="162" t="n">
         <v>601.7861167785649</v>
@@ -2238,7 +2238,7 @@
         <v>49.66158329374777</v>
       </c>
       <c r="Z10" s="162" t="n">
-        <v>56.80782031906144</v>
+        <v>56.80782031906145</v>
       </c>
       <c r="AA10" s="162" t="n">
         <v>64.96595308459942</v>
@@ -2253,7 +2253,7 @@
         <v>63020046.94088096</v>
       </c>
       <c r="AE10" s="165" t="n">
-        <v>73121067.08068278</v>
+        <v>73121067.0806828</v>
       </c>
       <c r="AF10" s="165" t="n">
         <v>84704424.20462692</v>
@@ -2318,7 +2318,7 @@
         </is>
       </c>
       <c r="C11" s="155" t="n">
-        <v>862.7521669320737</v>
+        <v>862.7521669320734</v>
       </c>
       <c r="D11" s="156" t="n">
         <v>944.4276090314042</v>
@@ -2333,7 +2333,7 @@
         <v>1173.253128344403</v>
       </c>
       <c r="H11" s="155" t="n">
-        <v>90.33626082261451</v>
+        <v>90.33626082261448</v>
       </c>
       <c r="I11" s="156" t="n">
         <v>101.9368459451843</v>
@@ -2348,7 +2348,7 @@
         <v>146.4987473324253</v>
       </c>
       <c r="M11" s="158" t="n">
-        <v>5785673.355077904</v>
+        <v>5785673.355077902</v>
       </c>
       <c r="N11" s="159" t="n">
         <v>6615844.724288275</v>
@@ -2368,7 +2368,7 @@
         </is>
       </c>
       <c r="T11" s="155" t="n">
-        <v>1115.283754559351</v>
+        <v>1115.28375455935</v>
       </c>
       <c r="U11" s="156" t="n">
         <v>1220.865979920493</v>
@@ -2398,7 +2398,7 @@
         <v>168.5231718594593</v>
       </c>
       <c r="AD11" s="158" t="n">
-        <v>5785673.355077904</v>
+        <v>5785673.355077902</v>
       </c>
       <c r="AE11" s="159" t="n">
         <v>6615844.724288275</v>
@@ -2464,13 +2464,13 @@
         <v>441.3701511308979</v>
       </c>
       <c r="D12" s="162" t="n">
-        <v>484.5670739048345</v>
+        <v>484.5670739048346</v>
       </c>
       <c r="E12" s="162" t="n">
         <v>529.9507853868749</v>
       </c>
       <c r="F12" s="162" t="n">
-        <v>565.7876120372732</v>
+        <v>565.7876120372733</v>
       </c>
       <c r="G12" s="163" t="n">
         <v>608.3536715191402</v>
@@ -2485,7 +2485,7 @@
         <v>57.11221157929113</v>
       </c>
       <c r="K12" s="162" t="n">
-        <v>64.39011985938906</v>
+        <v>64.39011985938907</v>
       </c>
       <c r="L12" s="163" t="n">
         <v>73.60863337917638</v>
@@ -2511,7 +2511,7 @@
         </is>
       </c>
       <c r="T12" s="161" t="n">
-        <v>524.1756014767407</v>
+        <v>524.1756014767406</v>
       </c>
       <c r="U12" s="162" t="n">
         <v>575.8821471631542</v>
@@ -2526,7 +2526,7 @@
         <v>723.1249037892422</v>
       </c>
       <c r="Y12" s="161" t="n">
-        <v>51.93641543463087</v>
+        <v>51.93641543463086</v>
       </c>
       <c r="Z12" s="162" t="n">
         <v>59.34107958056073</v>
@@ -2535,10 +2535,10 @@
         <v>67.78866155394313</v>
       </c>
       <c r="AB12" s="162" t="n">
-        <v>76.43903011266229</v>
+        <v>76.43903011266231</v>
       </c>
       <c r="AC12" s="163" t="n">
-        <v>87.39695020933091</v>
+        <v>87.39695020933092</v>
       </c>
       <c r="AD12" s="164" t="n">
         <v>68805720.29595886</v>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C13" s="155" t="n">
-        <v>9582.498635188995</v>
+        <v>9582.498635188993</v>
       </c>
       <c r="D13" s="156" t="n">
         <v>10043.46708596312</v>
@@ -2618,7 +2618,7 @@
         <v>11896.28817423528</v>
       </c>
       <c r="H13" s="155" t="n">
-        <v>9456.751573319389</v>
+        <v>9456.751573319387</v>
       </c>
       <c r="I13" s="156" t="n">
         <v>9692.033125865441</v>
@@ -2633,7 +2633,7 @@
         <v>11412.51492273603</v>
       </c>
       <c r="M13" s="158" t="n">
-        <v>62686425.14240307</v>
+        <v>62686425.14240306</v>
       </c>
       <c r="N13" s="159" t="n">
         <v>69553378.21742697</v>
@@ -2653,7 +2653,7 @@
         </is>
       </c>
       <c r="T13" s="155" t="n">
-        <v>5380.825824614036</v>
+        <v>5380.825824614034</v>
       </c>
       <c r="U13" s="156" t="n">
         <v>5639.671772699975</v>
@@ -2665,10 +2665,10 @@
         <v>6283.882012774219</v>
       </c>
       <c r="X13" s="157" t="n">
-        <v>6680.079701750277</v>
+        <v>6680.079701750279</v>
       </c>
       <c r="Y13" s="155" t="n">
-        <v>5340.946821982815</v>
+        <v>5340.946821982813</v>
       </c>
       <c r="Z13" s="156" t="n">
         <v>5527.133826548041</v>
@@ -2680,10 +2680,10 @@
         <v>6127.887735366546</v>
       </c>
       <c r="AC13" s="157" t="n">
-        <v>6524.770948923348</v>
+        <v>6524.770948923349</v>
       </c>
       <c r="AD13" s="158" t="n">
-        <v>62686425.14240307</v>
+        <v>62686425.14240306</v>
       </c>
       <c r="AE13" s="159" t="n">
         <v>69553378.21742697</v>
@@ -2746,10 +2746,10 @@
         </is>
       </c>
       <c r="C14" s="167" t="n">
-        <v>809.516417689592</v>
+        <v>809.5164176895919</v>
       </c>
       <c r="D14" s="168" t="n">
-        <v>870.6083669755369</v>
+        <v>870.608366975537</v>
       </c>
       <c r="E14" s="168" t="n">
         <v>945.8536563740383</v>
@@ -2764,7 +2764,7 @@
         <v>83.30308939036649</v>
       </c>
       <c r="I14" s="168" t="n">
-        <v>93.20209818781647</v>
+        <v>93.2020981878165</v>
       </c>
       <c r="J14" s="168" t="n">
         <v>105.7890546559377</v>
@@ -2779,7 +2779,7 @@
         <v>131492145.4383619</v>
       </c>
       <c r="N14" s="171" t="n">
-        <v>149290290.022398</v>
+        <v>149290290.0223981</v>
       </c>
       <c r="O14" s="171" t="n">
         <v>171727296.0080398</v>
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="T14" s="167" t="n">
-        <v>920.0749568834891</v>
+        <v>920.074956883489</v>
       </c>
       <c r="U14" s="168" t="n">
-        <v>990.0323498949411</v>
+        <v>990.0323498949414</v>
       </c>
       <c r="V14" s="168" t="n">
         <v>1075.080792309599</v>
@@ -2814,7 +2814,7 @@
         <v>98.38221752796859</v>
       </c>
       <c r="Z14" s="168" t="n">
-        <v>110.0726168959425</v>
+        <v>110.0726168959426</v>
       </c>
       <c r="AA14" s="168" t="n">
         <v>124.9207680194449</v>
@@ -2829,7 +2829,7 @@
         <v>131492145.4383619</v>
       </c>
       <c r="AE14" s="171" t="n">
-        <v>149290290.022398</v>
+        <v>149290290.0223981</v>
       </c>
       <c r="AF14" s="171" t="n">
         <v>171727296.0080398</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="C23" s="85" t="n">
-        <v>155891.194997355</v>
+        <v>155891.1949973551</v>
       </c>
       <c r="D23" s="86" t="n">
         <v>164552.8887516423</v>
@@ -3783,7 +3783,7 @@
         <v>1228911.857167671</v>
       </c>
       <c r="AD23" s="85" t="n">
-        <v>1324806.876257379</v>
+        <v>1324806.87625738</v>
       </c>
       <c r="AE23" s="86" t="n">
         <v>1343705.108983081</v>
@@ -3942,7 +3942,7 @@
         </is>
       </c>
       <c r="C25" s="91" t="n">
-        <v>162432.9569666398</v>
+        <v>162432.9569666399</v>
       </c>
       <c r="D25" s="92" t="n">
         <v>171478.1245912296</v>
@@ -4411,7 +4411,7 @@
         <v>370.9978892145276</v>
       </c>
       <c r="D35" s="149" t="n">
-        <v>418.3876078943426</v>
+        <v>418.3876078943427</v>
       </c>
       <c r="E35" s="149" t="n">
         <v>461.8198365449504</v>
@@ -4426,7 +4426,7 @@
         <v>39.02551586090905</v>
       </c>
       <c r="I35" s="149" t="n">
-        <v>45.95230405396983</v>
+        <v>45.95230405396984</v>
       </c>
       <c r="J35" s="149" t="n">
         <v>53.01581442880173</v>
@@ -4441,7 +4441,7 @@
         <v>48290754.3314328</v>
       </c>
       <c r="N35" s="152" t="n">
-        <v>57778530.06332078</v>
+        <v>57778530.06332079</v>
       </c>
       <c r="O35" s="152" t="n">
         <v>67623576.82618859</v>
@@ -4461,7 +4461,7 @@
         <v>449.9495478066943</v>
       </c>
       <c r="U35" s="149" t="n">
-        <v>507.4242211419361</v>
+        <v>507.4242211419362</v>
       </c>
       <c r="V35" s="149" t="n">
         <v>560.0992152853063</v>
@@ -4476,7 +4476,7 @@
         <v>48.3037547520585</v>
       </c>
       <c r="Z35" s="149" t="n">
-        <v>56.87130733965672</v>
+        <v>56.87130733965674</v>
       </c>
       <c r="AA35" s="149" t="n">
         <v>65.60573513971048</v>
@@ -4491,7 +4491,7 @@
         <v>48290754.3314328</v>
       </c>
       <c r="AE35" s="152" t="n">
-        <v>57778530.06332078</v>
+        <v>57778530.06332079</v>
       </c>
       <c r="AF35" s="152" t="n">
         <v>67623576.82618859</v>
@@ -4513,7 +4513,7 @@
         <v>867.9511022620006</v>
       </c>
       <c r="D36" s="156" t="n">
-        <v>985.9378096882504</v>
+        <v>985.9378096882501</v>
       </c>
       <c r="E36" s="156" t="n">
         <v>1087.877721456032</v>
@@ -4528,13 +4528,13 @@
         <v>61.05638798061553</v>
       </c>
       <c r="I36" s="156" t="n">
-        <v>70.40877805062682</v>
+        <v>70.40877805062681</v>
       </c>
       <c r="J36" s="156" t="n">
-        <v>80.55757800466613</v>
+        <v>80.55757800466615</v>
       </c>
       <c r="K36" s="156" t="n">
-        <v>91.42927303681414</v>
+        <v>91.42927303681417</v>
       </c>
       <c r="L36" s="157" t="n">
         <v>104.2168409402589</v>
@@ -4546,10 +4546,10 @@
         <v>19176155.71587607</v>
       </c>
       <c r="O36" s="159" t="n">
-        <v>22091121.32438299</v>
+        <v>22091121.324383</v>
       </c>
       <c r="P36" s="159" t="n">
-        <v>25225005.56477148</v>
+        <v>25225005.56477149</v>
       </c>
       <c r="Q36" s="160" t="n">
         <v>28995929.61161191</v>
@@ -4563,13 +4563,13 @@
         <v>880.3757914972617</v>
       </c>
       <c r="U36" s="156" t="n">
-        <v>1000.051474454325</v>
+        <v>1000.051474454324</v>
       </c>
       <c r="V36" s="156" t="n">
         <v>1103.450652442385</v>
       </c>
       <c r="W36" s="156" t="n">
-        <v>1177.803616517867</v>
+        <v>1177.803616517868</v>
       </c>
       <c r="X36" s="157" t="n">
         <v>1250.880068873116</v>
@@ -4578,13 +4578,13 @@
         <v>61.31262074650016</v>
       </c>
       <c r="Z36" s="156" t="n">
-        <v>70.70506955680909</v>
+        <v>70.70506955680908</v>
       </c>
       <c r="AA36" s="156" t="n">
-        <v>80.89886661682267</v>
+        <v>80.8988666168227</v>
       </c>
       <c r="AB36" s="156" t="n">
-        <v>91.82123953491487</v>
+        <v>91.82123953491489</v>
       </c>
       <c r="AC36" s="157" t="n">
         <v>104.6701093899213</v>
@@ -4596,10 +4596,10 @@
         <v>19176155.71587607</v>
       </c>
       <c r="AF36" s="159" t="n">
-        <v>22091121.32438299</v>
+        <v>22091121.324383</v>
       </c>
       <c r="AG36" s="159" t="n">
-        <v>25225005.56477148</v>
+        <v>25225005.56477149</v>
       </c>
       <c r="AH36" s="160" t="n">
         <v>28995929.61161191</v>
@@ -4615,7 +4615,7 @@
         <v>434.3578442417721</v>
       </c>
       <c r="D37" s="162" t="n">
-        <v>488.4530873384691</v>
+        <v>488.4530873384692</v>
       </c>
       <c r="E37" s="162" t="n">
         <v>538.0672521757167</v>
@@ -4645,7 +4645,7 @@
         <v>64799730.83190742</v>
       </c>
       <c r="N37" s="165" t="n">
-        <v>76954685.77919684</v>
+        <v>76954685.77919686</v>
       </c>
       <c r="O37" s="165" t="n">
         <v>89714698.15057158</v>
@@ -4665,7 +4665,7 @@
         <v>513.9694328062945</v>
       </c>
       <c r="U37" s="162" t="n">
-        <v>578.4262114919969</v>
+        <v>578.426211491997</v>
       </c>
       <c r="V37" s="162" t="n">
         <v>637.3818171240748</v>
@@ -4695,7 +4695,7 @@
         <v>64799730.83190742</v>
       </c>
       <c r="AE37" s="165" t="n">
-        <v>76954685.77919684</v>
+        <v>76954685.77919686</v>
       </c>
       <c r="AF37" s="165" t="n">
         <v>89714698.15057158</v>
@@ -4714,7 +4714,7 @@
         </is>
       </c>
       <c r="C38" s="155" t="n">
-        <v>887.1898354573775</v>
+        <v>887.1898354573772</v>
       </c>
       <c r="D38" s="156" t="n">
         <v>994.033275500011</v>
@@ -4729,7 +4729,7 @@
         <v>1261.732447373229</v>
       </c>
       <c r="H38" s="155" t="n">
-        <v>92.89505775458703</v>
+        <v>92.895057754587</v>
       </c>
       <c r="I38" s="156" t="n">
         <v>107.2910362848808</v>
@@ -4744,7 +4744,7 @@
         <v>157.5467548675427</v>
       </c>
       <c r="M38" s="158" t="n">
-        <v>5949553.983914629</v>
+        <v>5949553.983914627</v>
       </c>
       <c r="N38" s="159" t="n">
         <v>6963339.210538754</v>
@@ -4764,7 +4764,7 @@
         </is>
       </c>
       <c r="T38" s="155" t="n">
-        <v>1146.874442766482</v>
+        <v>1146.874442766481</v>
       </c>
       <c r="U38" s="156" t="n">
         <v>1284.99145658346</v>
@@ -4794,7 +4794,7 @@
         <v>181.2321219798341</v>
       </c>
       <c r="AD38" s="158" t="n">
-        <v>5949553.983914629</v>
+        <v>5949553.983914627</v>
       </c>
       <c r="AE38" s="159" t="n">
         <v>6963339.210538754</v>
@@ -4816,13 +4816,13 @@
         </is>
       </c>
       <c r="C39" s="161" t="n">
-        <v>453.8375936949001</v>
+        <v>453.8375936949</v>
       </c>
       <c r="D39" s="162" t="n">
-        <v>509.9760060511126</v>
+        <v>509.9760060511127</v>
       </c>
       <c r="E39" s="162" t="n">
-        <v>561.3020795028058</v>
+        <v>561.3020795028057</v>
       </c>
       <c r="F39" s="162" t="n">
         <v>606.8625767563703</v>
@@ -4840,7 +4840,7 @@
         <v>60.4909059641414</v>
       </c>
       <c r="K39" s="162" t="n">
-        <v>69.06470418257604</v>
+        <v>69.06470418257605</v>
       </c>
       <c r="L39" s="163" t="n">
         <v>79.15125086801071</v>
@@ -4866,7 +4866,7 @@
         </is>
       </c>
       <c r="T39" s="161" t="n">
-        <v>538.9820608354398</v>
+        <v>538.9820608354397</v>
       </c>
       <c r="U39" s="162" t="n">
         <v>606.0793091032065</v>
@@ -4881,7 +4881,7 @@
         <v>777.5751028264618</v>
       </c>
       <c r="Y39" s="161" t="n">
-        <v>53.40347041048804</v>
+        <v>53.40347041048803</v>
       </c>
       <c r="Z39" s="162" t="n">
         <v>62.45270962260829</v>
@@ -4890,10 +4890,10 @@
         <v>71.79896274549901</v>
       </c>
       <c r="AB39" s="162" t="n">
-        <v>81.98833942633591</v>
+        <v>81.98833942633594</v>
       </c>
       <c r="AC39" s="163" t="n">
-        <v>93.977806862459</v>
+        <v>93.97780686245902</v>
       </c>
       <c r="AD39" s="164" t="n">
         <v>70749284.81582205</v>
@@ -4918,7 +4918,7 @@
         </is>
       </c>
       <c r="C40" s="155" t="n">
-        <v>9856.509602128159</v>
+        <v>9856.509602128157</v>
       </c>
       <c r="D40" s="156" t="n">
         <v>10573.18358349628</v>
@@ -4930,10 +4930,10 @@
         <v>12007.20544274847</v>
       </c>
       <c r="G40" s="157" t="n">
-        <v>12795.83540307118</v>
+        <v>12795.83540307119</v>
       </c>
       <c r="H40" s="155" t="n">
-        <v>9727.166810655615</v>
+        <v>9727.166810655614</v>
       </c>
       <c r="I40" s="156" t="n">
         <v>10203.21415503257</v>
@@ -4948,7 +4948,7 @@
         <v>12275.4812549597</v>
       </c>
       <c r="M40" s="158" t="n">
-        <v>64478939.66509265</v>
+        <v>64478939.66509264</v>
       </c>
       <c r="N40" s="159" t="n">
         <v>73221789.89096428</v>
@@ -4968,7 +4968,7 @@
         </is>
       </c>
       <c r="T40" s="155" t="n">
-        <v>5534.690212522152</v>
+        <v>5534.69021252215</v>
       </c>
       <c r="U40" s="156" t="n">
         <v>5937.121563006606</v>
@@ -4980,10 +4980,10 @@
         <v>6742.362674650451</v>
       </c>
       <c r="X40" s="157" t="n">
-        <v>7185.199205926941</v>
+        <v>7185.199205926943</v>
       </c>
       <c r="Y40" s="155" t="n">
-        <v>5493.670872230832</v>
+        <v>5493.67087223083</v>
       </c>
       <c r="Z40" s="156" t="n">
         <v>5818.648096165955</v>
@@ -4995,10 +4995,10 @@
         <v>6574.986840522045</v>
       </c>
       <c r="AC40" s="157" t="n">
-        <v>7018.146659054908</v>
+        <v>7018.14665905491</v>
       </c>
       <c r="AD40" s="158" t="n">
-        <v>64478939.66509265</v>
+        <v>64478939.66509264</v>
       </c>
       <c r="AE40" s="159" t="n">
         <v>73221789.89096428</v>
@@ -5020,10 +5020,10 @@
         </is>
       </c>
       <c r="C41" s="179" t="n">
-        <v>832.517162811286</v>
+        <v>832.5171628112856</v>
       </c>
       <c r="D41" s="180" t="n">
-        <v>916.3840300638382</v>
+        <v>916.3840300638379</v>
       </c>
       <c r="E41" s="180" t="n">
         <v>1001.978955572851</v>
@@ -5035,10 +5035,10 @@
         <v>1168.479219973015</v>
       </c>
       <c r="H41" s="179" t="n">
-        <v>85.66997545351268</v>
+        <v>85.66997545351265</v>
       </c>
       <c r="I41" s="180" t="n">
-        <v>98.10256550194251</v>
+        <v>98.10256550194249</v>
       </c>
       <c r="J41" s="180" t="n">
         <v>112.0663918576412</v>
@@ -5062,7 +5062,7 @@
         <v>210325023.5573645</v>
       </c>
       <c r="Q41" s="184" t="n">
-        <v>245031241.763503</v>
+        <v>245031241.7635031</v>
       </c>
       <c r="S41" s="51" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="T41" s="185" t="n">
-        <v>946.2169956534124</v>
+        <v>946.216995653412</v>
       </c>
       <c r="U41" s="186" t="n">
         <v>1042.087199141047</v>
@@ -5112,7 +5112,7 @@
         <v>210325023.5573645</v>
       </c>
       <c r="AH41" s="190" t="n">
-        <v>245031241.763503</v>
+        <v>245031241.7635031</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" thickBot="1"/>
@@ -5695,7 +5695,7 @@
         <v>0.02110910401598939</v>
       </c>
       <c r="I49" s="156" t="n">
-        <v>0.02287827782149928</v>
+        <v>0.02287827782149927</v>
       </c>
       <c r="J49" s="156" t="n">
         <v>0.02497553761713669</v>
@@ -5713,7 +5713,7 @@
         <v>1484.832419747022</v>
       </c>
       <c r="O49" s="159" t="n">
-        <v>1641.567189502637</v>
+        <v>1641.567189502636</v>
       </c>
       <c r="P49" s="159" t="n">
         <v>1823.946352707848</v>
@@ -5730,10 +5730,10 @@
         <v>0.2606111938656079</v>
       </c>
       <c r="U49" s="156" t="n">
-        <v>0.2740060359181392</v>
+        <v>0.2740060359181391</v>
       </c>
       <c r="V49" s="156" t="n">
-        <v>0.2881456291855614</v>
+        <v>0.2881456291855613</v>
       </c>
       <c r="W49" s="156" t="n">
         <v>0.3001463146460073</v>
@@ -5745,7 +5745,7 @@
         <v>0.02422117392838157</v>
       </c>
       <c r="Z49" s="156" t="n">
-        <v>0.0262618143346402</v>
+        <v>0.02626181433464019</v>
       </c>
       <c r="AA49" s="156" t="n">
         <v>0.02868405726235716</v>
@@ -5763,7 +5763,7 @@
         <v>1484.832419747022</v>
       </c>
       <c r="AF49" s="159" t="n">
-        <v>1641.567189502637</v>
+        <v>1641.567189502636</v>
       </c>
       <c r="AG49" s="159" t="n">
         <v>1823.946352707848</v>
@@ -5782,10 +5782,10 @@
         <v>0.1329022787823142</v>
       </c>
       <c r="D50" s="162" t="n">
-        <v>0.148392056366162</v>
+        <v>0.1483920563661621</v>
       </c>
       <c r="E50" s="162" t="n">
-        <v>0.165981017056577</v>
+        <v>0.1659810170565769</v>
       </c>
       <c r="F50" s="162" t="n">
         <v>0.1841802972031953</v>
@@ -5856,7 +5856,7 @@
         <v>0.02488312395773463</v>
       </c>
       <c r="AC50" s="163" t="n">
-        <v>0.02917939240394735</v>
+        <v>0.02917939240394736</v>
       </c>
       <c r="AD50" s="164" t="n">
         <v>20718.29505724658</v>
@@ -6334,13 +6334,13 @@
         </is>
       </c>
       <c r="C57" s="148" t="n">
-        <v>0.008182027449917733</v>
+        <v>0.00818202744991773</v>
       </c>
       <c r="D57" s="149" t="n">
-        <v>0.007633940756100645</v>
+        <v>0.00763394075610065</v>
       </c>
       <c r="E57" s="149" t="n">
-        <v>0.007123300657313042</v>
+        <v>0.007123300657313039</v>
       </c>
       <c r="F57" s="149" t="n">
         <v>0.0002614860757246538</v>
@@ -6349,13 +6349,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="148" t="n">
-        <v>0.0008606729345473974</v>
+        <v>0.0008606729345473971</v>
       </c>
       <c r="I57" s="149" t="n">
-        <v>0.000838450183837466</v>
+        <v>0.0008384501838374665</v>
       </c>
       <c r="J57" s="149" t="n">
-        <v>0.0008177379053138875</v>
+        <v>0.000817737905313887</v>
       </c>
       <c r="K57" s="149" t="n">
         <v>3.165848129811418e-05</v>
@@ -6367,10 +6367,10 @@
         <v>1065.009502759038</v>
       </c>
       <c r="N57" s="152" t="n">
-        <v>1054.23264732391</v>
+        <v>1054.232647323911</v>
       </c>
       <c r="O57" s="152" t="n">
-        <v>1043.054089793223</v>
+        <v>1043.054089793222</v>
       </c>
       <c r="P57" s="152" t="n">
         <v>40.92110070816573</v>
@@ -6384,13 +6384,13 @@
         </is>
       </c>
       <c r="T57" s="148" t="n">
-        <v>0.009923235841117243</v>
+        <v>0.009923235841117237</v>
       </c>
       <c r="U57" s="149" t="n">
-        <v>0.009258511412188582</v>
+        <v>0.009258511412188588</v>
       </c>
       <c r="V57" s="149" t="n">
-        <v>0.00863920254758049</v>
+        <v>0.008639202547580487</v>
       </c>
       <c r="W57" s="149" t="n">
         <v>0.0003171326440135655</v>
@@ -6417,10 +6417,10 @@
         <v>1065.009502759038</v>
       </c>
       <c r="AE57" s="152" t="n">
-        <v>1054.23264732391</v>
+        <v>1054.232647323911</v>
       </c>
       <c r="AF57" s="152" t="n">
-        <v>1043.054089793223</v>
+        <v>1043.054089793222</v>
       </c>
       <c r="AG57" s="152" t="n">
         <v>40.92110070816573</v>
@@ -6538,13 +6538,13 @@
         </is>
       </c>
       <c r="C59" s="161" t="n">
-        <v>0.00713884495778855</v>
+        <v>0.007138844957788546</v>
       </c>
       <c r="D59" s="162" t="n">
-        <v>0.006691511844202422</v>
+        <v>0.006691511844202427</v>
       </c>
       <c r="E59" s="162" t="n">
-        <v>0.006255755851998115</v>
+        <v>0.006255755851998113</v>
       </c>
       <c r="F59" s="162" t="n">
         <v>0.0002296126791426051</v>
@@ -6553,13 +6553,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="161" t="n">
-        <v>0.0007063315740046652</v>
+        <v>0.0007063315740046649</v>
       </c>
       <c r="I59" s="162" t="n">
-        <v>0.0006891700716674463</v>
+        <v>0.0006891700716674467</v>
       </c>
       <c r="J59" s="162" t="n">
-        <v>0.0006730407428210299</v>
+        <v>0.0006730407428210296</v>
       </c>
       <c r="K59" s="162" t="n">
         <v>2.608972433167517e-05</v>
@@ -6571,10 +6571,10 @@
         <v>1065.009502759038</v>
       </c>
       <c r="N59" s="165" t="n">
-        <v>1054.23264732391</v>
+        <v>1054.232647323911</v>
       </c>
       <c r="O59" s="165" t="n">
-        <v>1043.054089793223</v>
+        <v>1043.054089793222</v>
       </c>
       <c r="P59" s="165" t="n">
         <v>40.92110070816573</v>
@@ -6588,13 +6588,13 @@
         </is>
       </c>
       <c r="T59" s="161" t="n">
-        <v>0.00844729326864496</v>
+        <v>0.008447293268644957</v>
       </c>
       <c r="U59" s="162" t="n">
-        <v>0.007924089222746122</v>
+        <v>0.007924089222746128</v>
       </c>
       <c r="V59" s="162" t="n">
-        <v>0.007410421311291751</v>
+        <v>0.007410421311291747</v>
       </c>
       <c r="W59" s="162" t="n">
         <v>0.0002719883976691478</v>
@@ -6603,13 +6603,13 @@
         <v>0</v>
       </c>
       <c r="Y59" s="161" t="n">
-        <v>0.0008392576758871188</v>
+        <v>0.0008392576758871185</v>
       </c>
       <c r="Z59" s="162" t="n">
-        <v>0.0008190342564008701</v>
+        <v>0.0008190342564008706</v>
       </c>
       <c r="AA59" s="162" t="n">
-        <v>0.0007999936685539095</v>
+        <v>0.0007999936685539092</v>
       </c>
       <c r="AB59" s="162" t="n">
         <v>3.101495370681969e-05</v>
@@ -6621,10 +6621,10 @@
         <v>1065.009502759038</v>
       </c>
       <c r="AE59" s="165" t="n">
-        <v>1054.23264732391</v>
+        <v>1054.232647323911</v>
       </c>
       <c r="AF59" s="165" t="n">
-        <v>1043.054089793223</v>
+        <v>1043.054089793222</v>
       </c>
       <c r="AG59" s="165" t="n">
         <v>40.92110070816573</v>
@@ -6742,13 +6742,13 @@
         </is>
       </c>
       <c r="C61" s="161" t="n">
-        <v>0.00683174891806499</v>
+        <v>0.006831748918064985</v>
       </c>
       <c r="D61" s="162" t="n">
-        <v>0.006406649286571023</v>
+        <v>0.006406649286571029</v>
       </c>
       <c r="E61" s="162" t="n">
-        <v>0.005991132696581464</v>
+        <v>0.005991132696581461</v>
       </c>
       <c r="F61" s="162" t="n">
         <v>0.0002199189779151274</v>
@@ -6757,13 +6757,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="161" t="n">
-        <v>0.0006775516689296475</v>
+        <v>0.0006775516689296472</v>
       </c>
       <c r="I61" s="162" t="n">
-        <v>0.0006611205960326975</v>
+        <v>0.000661120596032698</v>
       </c>
       <c r="J61" s="162" t="n">
-        <v>0.0006456577621957494</v>
+        <v>0.0006456577621957492</v>
       </c>
       <c r="K61" s="162" t="n">
         <v>2.502813608152401e-05</v>
@@ -6775,10 +6775,10 @@
         <v>1065.009502759038</v>
       </c>
       <c r="N61" s="165" t="n">
-        <v>1054.23264732391</v>
+        <v>1054.232647323911</v>
       </c>
       <c r="O61" s="165" t="n">
-        <v>1043.054089793223</v>
+        <v>1043.054089793222</v>
       </c>
       <c r="P61" s="165" t="n">
         <v>40.92110070816573</v>
@@ -6792,13 +6792,13 @@
         </is>
       </c>
       <c r="T61" s="161" t="n">
-        <v>0.008113453275191583</v>
+        <v>0.008113453275191577</v>
       </c>
       <c r="U61" s="162" t="n">
-        <v>0.007613961298568128</v>
+        <v>0.007613961298568133</v>
       </c>
       <c r="V61" s="162" t="n">
-        <v>0.00712215485530115</v>
+        <v>0.007122154855301146</v>
       </c>
       <c r="W61" s="162" t="n">
         <v>0.0002614290763594635</v>
@@ -6807,16 +6807,16 @@
         <v>0</v>
       </c>
       <c r="Y61" s="161" t="n">
-        <v>0.0008038979279513732</v>
+        <v>0.0008038979279513727</v>
       </c>
       <c r="Z61" s="162" t="n">
-        <v>0.0007845714363040233</v>
+        <v>0.0007845714363040238</v>
       </c>
       <c r="AA61" s="162" t="n">
-        <v>0.0007663558162232738</v>
+        <v>0.0007663558162232735</v>
       </c>
       <c r="AB61" s="162" t="n">
-        <v>2.971149070349898e-05</v>
+        <v>2.971149070349899e-05</v>
       </c>
       <c r="AC61" s="163" t="n">
         <v>0</v>
@@ -6825,10 +6825,10 @@
         <v>1065.009502759038</v>
       </c>
       <c r="AE61" s="165" t="n">
-        <v>1054.23264732391</v>
+        <v>1054.232647323911</v>
       </c>
       <c r="AF61" s="165" t="n">
-        <v>1043.054089793223</v>
+        <v>1043.054089793222</v>
       </c>
       <c r="AG61" s="165" t="n">
         <v>40.92110070816573</v>
@@ -6946,13 +6946,13 @@
         </is>
       </c>
       <c r="C63" s="179" t="n">
-        <v>0.006556609709307749</v>
+        <v>0.006556609709307744</v>
       </c>
       <c r="D63" s="180" t="n">
-        <v>0.006147913326186622</v>
+        <v>0.006147913326186626</v>
       </c>
       <c r="E63" s="180" t="n">
-        <v>0.005745018686957173</v>
+        <v>0.00574501868695717</v>
       </c>
       <c r="F63" s="180" t="n">
         <v>0.0002107318399543467</v>
@@ -6961,13 +6961,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="179" t="n">
-        <v>0.0006747063219187761</v>
+        <v>0.0006747063219187758</v>
       </c>
       <c r="I63" s="180" t="n">
-        <v>0.0006581586430969041</v>
+        <v>0.0006581586430969047</v>
       </c>
       <c r="J63" s="180" t="n">
-        <v>0.0006425519336720273</v>
+        <v>0.0006425519336720269</v>
       </c>
       <c r="K63" s="180" t="n">
         <v>2.489899839841275e-05</v>
@@ -6979,10 +6979,10 @@
         <v>1065.009502759038</v>
       </c>
       <c r="N63" s="183" t="n">
-        <v>1054.23264732391</v>
+        <v>1054.232647323911</v>
       </c>
       <c r="O63" s="183" t="n">
-        <v>1043.054089793223</v>
+        <v>1043.054089793222</v>
       </c>
       <c r="P63" s="183" t="n">
         <v>40.92110070816573</v>
@@ -6996,13 +6996,13 @@
         </is>
       </c>
       <c r="T63" s="185" t="n">
-        <v>0.007452069240066203</v>
+        <v>0.007452069240066198</v>
       </c>
       <c r="U63" s="186" t="n">
-        <v>0.006991241191972134</v>
+        <v>0.006991241191972139</v>
       </c>
       <c r="V63" s="186" t="n">
-        <v>0.006529931137005539</v>
+        <v>0.006529931137005536</v>
       </c>
       <c r="W63" s="186" t="n">
         <v>0.0002393395892500571</v>
@@ -7011,13 +7011,13 @@
         <v>0</v>
       </c>
       <c r="Y63" s="185" t="n">
-        <v>0.0007968384440035543</v>
+        <v>0.000796838444003554</v>
       </c>
       <c r="Z63" s="186" t="n">
-        <v>0.0007772919879160947</v>
+        <v>0.0007772919879160952</v>
       </c>
       <c r="AA63" s="186" t="n">
-        <v>0.0007587560103240213</v>
+        <v>0.000758756010324021</v>
       </c>
       <c r="AB63" s="186" t="n">
         <v>2.93953088840799e-05</v>
@@ -7029,10 +7029,10 @@
         <v>1065.009502759038</v>
       </c>
       <c r="AE63" s="189" t="n">
-        <v>1054.23264732391</v>
+        <v>1054.232647323911</v>
       </c>
       <c r="AF63" s="189" t="n">
-        <v>1043.054089793223</v>
+        <v>1043.054089793222</v>
       </c>
       <c r="AG63" s="189" t="n">
         <v>40.92110070816573</v>
@@ -7297,43 +7297,43 @@
         </is>
       </c>
       <c r="C68" s="148" t="n">
-        <v>0.003472795405995926</v>
+        <v>0.003472795405995924</v>
       </c>
       <c r="D68" s="149" t="n">
-        <v>0.005116953584883509</v>
+        <v>0.005116953584883512</v>
       </c>
       <c r="E68" s="149" t="n">
-        <v>0.006822884135009858</v>
+        <v>0.006822884135009856</v>
       </c>
       <c r="F68" s="149" t="n">
         <v>0.008413407190420016</v>
       </c>
       <c r="G68" s="150" t="n">
-        <v>0.009940226928103984</v>
+        <v>0.009940226928103982</v>
       </c>
       <c r="H68" s="148" t="n">
-        <v>0.0003653056692190988</v>
+        <v>0.0003653056692190986</v>
       </c>
       <c r="I68" s="149" t="n">
-        <v>0.0005620047117217629</v>
+        <v>0.0005620047117217631</v>
       </c>
       <c r="J68" s="149" t="n">
-        <v>0.0007832508059356401</v>
+        <v>0.00078325080593564</v>
       </c>
       <c r="K68" s="149" t="n">
         <v>0.001018622859565973</v>
       </c>
       <c r="L68" s="150" t="n">
-        <v>0.001277558751988083</v>
+        <v>0.001277558751988082</v>
       </c>
       <c r="M68" s="151" t="n">
-        <v>452.0346736994608</v>
+        <v>452.0346736994605</v>
       </c>
       <c r="N68" s="152" t="n">
-        <v>706.6415232151685</v>
+        <v>706.6415232151688</v>
       </c>
       <c r="O68" s="152" t="n">
-        <v>999.0645549828262</v>
+        <v>999.0645549828259</v>
       </c>
       <c r="P68" s="152" t="n">
         <v>1316.650922936784</v>
@@ -7347,13 +7347,13 @@
         </is>
       </c>
       <c r="T68" s="148" t="n">
-        <v>0.004211837231368927</v>
+        <v>0.004211837231368925</v>
       </c>
       <c r="U68" s="149" t="n">
-        <v>0.006205886929817124</v>
+        <v>0.006205886929817127</v>
       </c>
       <c r="V68" s="149" t="n">
-        <v>0.008274854710857853</v>
+        <v>0.008274854710857852</v>
       </c>
       <c r="W68" s="149" t="n">
         <v>0.01020385525334908</v>
@@ -7362,13 +7362,13 @@
         <v>0.01205559584413176</v>
       </c>
       <c r="Y68" s="148" t="n">
-        <v>0.0004521563665778771</v>
+        <v>0.0004521563665778769</v>
       </c>
       <c r="Z68" s="149" t="n">
-        <v>0.0006955460307088204</v>
+        <v>0.0006955460307088207</v>
       </c>
       <c r="AA68" s="149" t="n">
-        <v>0.0009692531459869871</v>
+        <v>0.0009692531459869869</v>
       </c>
       <c r="AB68" s="149" t="n">
         <v>0.001260338466649428</v>
@@ -7377,13 +7377,13 @@
         <v>0.001580448352649777</v>
       </c>
       <c r="AD68" s="151" t="n">
-        <v>452.0346736994608</v>
+        <v>452.0346736994605</v>
       </c>
       <c r="AE68" s="152" t="n">
-        <v>706.6415232151685</v>
+        <v>706.6415232151688</v>
       </c>
       <c r="AF68" s="152" t="n">
-        <v>999.0645549828262</v>
+        <v>999.0645549828259</v>
       </c>
       <c r="AG68" s="152" t="n">
         <v>1316.650922936784</v>
@@ -7501,28 +7501,28 @@
         </is>
       </c>
       <c r="C70" s="161" t="n">
-        <v>0.003030025030504453</v>
+        <v>0.003030025030504451</v>
       </c>
       <c r="D70" s="162" t="n">
-        <v>0.004485252979219038</v>
+        <v>0.00448525297921904</v>
       </c>
       <c r="E70" s="162" t="n">
-        <v>0.0059919269743688</v>
+        <v>0.005991926974368798</v>
       </c>
       <c r="F70" s="162" t="n">
         <v>0.007387869355400093</v>
       </c>
       <c r="G70" s="163" t="n">
-        <v>0.008725395758803501</v>
+        <v>0.0087253957588035</v>
       </c>
       <c r="H70" s="161" t="n">
-        <v>0.0002997967264626979</v>
+        <v>0.0002997967264626977</v>
       </c>
       <c r="I70" s="162" t="n">
-        <v>0.0004619437563744531</v>
+        <v>0.0004619437563744533</v>
       </c>
       <c r="J70" s="162" t="n">
-        <v>0.0006446560698928884</v>
+        <v>0.0006446560698928883</v>
       </c>
       <c r="K70" s="162" t="n">
         <v>0.0008394461298938541</v>
@@ -7531,13 +7531,13 @@
         <v>0.001054310171621722</v>
       </c>
       <c r="M70" s="164" t="n">
-        <v>452.0346736994608</v>
+        <v>452.0346736994605</v>
       </c>
       <c r="N70" s="165" t="n">
-        <v>706.6415232151685</v>
+        <v>706.6415232151688</v>
       </c>
       <c r="O70" s="165" t="n">
-        <v>999.0645549828262</v>
+        <v>999.0645549828259</v>
       </c>
       <c r="P70" s="165" t="n">
         <v>1316.650922936784</v>
@@ -7551,13 +7551,13 @@
         </is>
       </c>
       <c r="T70" s="161" t="n">
-        <v>0.003585385338293564</v>
+        <v>0.003585385338293562</v>
       </c>
       <c r="U70" s="162" t="n">
-        <v>0.005311437179135082</v>
+        <v>0.005311437179135085</v>
       </c>
       <c r="V70" s="162" t="n">
-        <v>0.007097895825391593</v>
+        <v>0.007097895825391591</v>
       </c>
       <c r="W70" s="162" t="n">
         <v>0.008751323122345033</v>
@@ -7566,13 +7566,13 @@
         <v>0.01033506129924573</v>
       </c>
       <c r="Y70" s="161" t="n">
-        <v>0.000356216135805913</v>
+        <v>0.0003562161358059129</v>
       </c>
       <c r="Z70" s="162" t="n">
-        <v>0.0005489904111560777</v>
+        <v>0.0005489904111560779</v>
       </c>
       <c r="AA70" s="162" t="n">
-        <v>0.0007662549107317476</v>
+        <v>0.0007662549107317475</v>
       </c>
       <c r="AB70" s="162" t="n">
         <v>0.0009979171311679073</v>
@@ -7581,13 +7581,13 @@
         <v>0.001253511853606745</v>
       </c>
       <c r="AD70" s="164" t="n">
-        <v>452.0346736994608</v>
+        <v>452.0346736994605</v>
       </c>
       <c r="AE70" s="165" t="n">
-        <v>706.6415232151685</v>
+        <v>706.6415232151688</v>
       </c>
       <c r="AF70" s="165" t="n">
-        <v>999.0645549828262</v>
+        <v>999.0645549828259</v>
       </c>
       <c r="AG70" s="165" t="n">
         <v>1316.650922936784</v>
@@ -7615,7 +7615,7 @@
         <v>0.02819359390889913</v>
       </c>
       <c r="G71" s="157" t="n">
-        <v>0.03353583984218844</v>
+        <v>0.03353583984218843</v>
       </c>
       <c r="H71" s="155" t="n">
         <v>0.001178300061841106</v>
@@ -7630,7 +7630,7 @@
         <v>0.003329073552465295</v>
       </c>
       <c r="L71" s="157" t="n">
-        <v>0.004187466803991569</v>
+        <v>0.004187466803991567</v>
       </c>
       <c r="M71" s="158" t="n">
         <v>75.46536916628854</v>
@@ -7645,7 +7645,7 @@
         <v>221.4770869309021</v>
       </c>
       <c r="Q71" s="160" t="n">
-        <v>282.7616920903298</v>
+        <v>282.7616920903297</v>
       </c>
       <c r="S71" s="32" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>0.03644599048768812</v>
       </c>
       <c r="X71" s="157" t="n">
-        <v>0.04335193674968971</v>
+        <v>0.04335193674968969</v>
       </c>
       <c r="Y71" s="155" t="n">
         <v>0.00135201431174238</v>
@@ -7674,13 +7674,13 @@
         <v>0.002088139771329722</v>
       </c>
       <c r="AA71" s="156" t="n">
-        <v>0.002922072920429461</v>
+        <v>0.002922072920429462</v>
       </c>
       <c r="AB71" s="156" t="n">
         <v>0.003826294258018308</v>
       </c>
       <c r="AC71" s="157" t="n">
-        <v>0.004817004928127866</v>
+        <v>0.004817004928127864</v>
       </c>
       <c r="AD71" s="158" t="n">
         <v>75.46536916628854</v>
@@ -7695,7 +7695,7 @@
         <v>221.4770869309021</v>
       </c>
       <c r="AH71" s="160" t="n">
-        <v>282.7616920903298</v>
+        <v>282.7616920903297</v>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1" thickTop="1">
@@ -7705,40 +7705,40 @@
         </is>
       </c>
       <c r="C72" s="161" t="n">
-        <v>0.003383770602789332</v>
+        <v>0.00338377060278933</v>
       </c>
       <c r="D72" s="162" t="n">
-        <v>0.005011787470122261</v>
+        <v>0.005011787470122263</v>
       </c>
       <c r="E72" s="162" t="n">
-        <v>0.00669899465653062</v>
+        <v>0.006698994656530619</v>
       </c>
       <c r="F72" s="162" t="n">
         <v>0.008266237563967348</v>
       </c>
       <c r="G72" s="163" t="n">
-        <v>0.009767096644808161</v>
+        <v>0.009767096644808159</v>
       </c>
       <c r="H72" s="161" t="n">
-        <v>0.0003355918735731824</v>
+        <v>0.0003355918735731822</v>
       </c>
       <c r="I72" s="162" t="n">
-        <v>0.0005171807869023895</v>
+        <v>0.0005171807869023897</v>
       </c>
       <c r="J72" s="162" t="n">
-        <v>0.000721943264812818</v>
+        <v>0.0007219432648128178</v>
       </c>
       <c r="K72" s="162" t="n">
         <v>0.0009407488184717926</v>
       </c>
       <c r="L72" s="163" t="n">
-        <v>0.001181784001256</v>
+        <v>0.001181784001255999</v>
       </c>
       <c r="M72" s="164" t="n">
-        <v>527.5000428657493</v>
+        <v>527.500042865749</v>
       </c>
       <c r="N72" s="165" t="n">
-        <v>824.7041060179032</v>
+        <v>824.7041060179035</v>
       </c>
       <c r="O72" s="165" t="n">
         <v>1166.292607403642</v>
@@ -7747,7 +7747,7 @@
         <v>1538.128009867686</v>
       </c>
       <c r="Q72" s="166" t="n">
-        <v>1961.409950895412</v>
+        <v>1961.409950895411</v>
       </c>
       <c r="S72" s="42" t="inlineStr">
         <is>
@@ -7755,13 +7755,13 @@
         </is>
       </c>
       <c r="T72" s="161" t="n">
-        <v>0.004018599777152544</v>
+        <v>0.004018599777152541</v>
       </c>
       <c r="U72" s="162" t="n">
-        <v>0.00595624235497732</v>
+        <v>0.005956242354977322</v>
       </c>
       <c r="V72" s="162" t="n">
-        <v>0.007963648901629242</v>
+        <v>0.00796364890162924</v>
       </c>
       <c r="W72" s="162" t="n">
         <v>0.009826504614576223</v>
@@ -7770,13 +7770,13 @@
         <v>0.01160974471303888</v>
       </c>
       <c r="Y72" s="161" t="n">
-        <v>0.0003981712748623054</v>
+        <v>0.0003981712748623052</v>
       </c>
       <c r="Z72" s="162" t="n">
-        <v>0.0006137537920370348</v>
+        <v>0.000613753792037035</v>
       </c>
       <c r="AA72" s="162" t="n">
-        <v>0.000856901987968022</v>
+        <v>0.0008569019879680219</v>
       </c>
       <c r="AB72" s="162" t="n">
         <v>0.001116785112695069</v>
@@ -7785,10 +7785,10 @@
         <v>0.00140315493950161</v>
       </c>
       <c r="AD72" s="164" t="n">
-        <v>527.5000428657493</v>
+        <v>527.500042865749</v>
       </c>
       <c r="AE72" s="165" t="n">
-        <v>824.7041060179032</v>
+        <v>824.7041060179035</v>
       </c>
       <c r="AF72" s="165" t="n">
         <v>1166.292607403642</v>
@@ -7797,7 +7797,7 @@
         <v>1538.128009867686</v>
       </c>
       <c r="AH72" s="166" t="n">
-        <v>1961.409950895412</v>
+        <v>1961.409950895411</v>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" thickBot="1">
@@ -7909,40 +7909,40 @@
         </is>
       </c>
       <c r="C74" s="179" t="n">
-        <v>0.003247493936677433</v>
+        <v>0.003247493936677431</v>
       </c>
       <c r="D74" s="180" t="n">
-        <v>0.004809383750748599</v>
+        <v>0.004809383750748601</v>
       </c>
       <c r="E74" s="180" t="n">
-        <v>0.006423801880995669</v>
+        <v>0.006423801880995668</v>
       </c>
       <c r="F74" s="180" t="n">
         <v>0.007920914638057499</v>
       </c>
       <c r="G74" s="181" t="n">
-        <v>0.009353365525860666</v>
+        <v>0.009353365525860665</v>
       </c>
       <c r="H74" s="179" t="n">
-        <v>0.0003341825709647884</v>
+        <v>0.0003341825709647883</v>
       </c>
       <c r="I74" s="180" t="n">
-        <v>0.0005148637131955742</v>
+        <v>0.0005148637131955744</v>
       </c>
       <c r="J74" s="180" t="n">
-        <v>0.0007184704776558272</v>
+        <v>0.000718470477655827</v>
       </c>
       <c r="K74" s="180" t="n">
-        <v>0.0009358948364408741</v>
+        <v>0.0009358948364408739</v>
       </c>
       <c r="L74" s="181" t="n">
         <v>0.001175227457718195</v>
       </c>
       <c r="M74" s="182" t="n">
-        <v>527.5000428657493</v>
+        <v>527.500042865749</v>
       </c>
       <c r="N74" s="183" t="n">
-        <v>824.7041060179032</v>
+        <v>824.7041060179035</v>
       </c>
       <c r="O74" s="183" t="n">
         <v>1166.292607403642</v>
@@ -7951,7 +7951,7 @@
         <v>1538.128009867686</v>
       </c>
       <c r="Q74" s="184" t="n">
-        <v>1961.409950895412</v>
+        <v>1961.409950895411</v>
       </c>
       <c r="S74" s="51" t="inlineStr">
         <is>
@@ -7959,13 +7959,13 @@
         </is>
       </c>
       <c r="T74" s="185" t="n">
-        <v>0.00369101574529598</v>
+        <v>0.003691015745295978</v>
       </c>
       <c r="U74" s="186" t="n">
-        <v>0.005469101466186544</v>
+        <v>0.005469101466186546</v>
       </c>
       <c r="V74" s="186" t="n">
-        <v>0.007301452998908421</v>
+        <v>0.007301452998908419</v>
       </c>
       <c r="W74" s="186" t="n">
         <v>0.008996212705057544</v>
@@ -7974,25 +7974,25 @@
         <v>0.01061574182593037</v>
       </c>
       <c r="Y74" s="185" t="n">
-        <v>0.000394674706920482</v>
+        <v>0.0003946747069204819</v>
       </c>
       <c r="Z74" s="186" t="n">
-        <v>0.0006080592321215273</v>
+        <v>0.0006080592321215275</v>
       </c>
       <c r="AA74" s="186" t="n">
-        <v>0.0008484042527836868</v>
+        <v>0.0008484042527836866</v>
       </c>
       <c r="AB74" s="186" t="n">
         <v>0.001104900581139388</v>
       </c>
       <c r="AC74" s="187" t="n">
-        <v>0.001387084068520583</v>
+        <v>0.001387084068520582</v>
       </c>
       <c r="AD74" s="188" t="n">
-        <v>527.5000428657493</v>
+        <v>527.500042865749</v>
       </c>
       <c r="AE74" s="189" t="n">
-        <v>824.7041060179032</v>
+        <v>824.7041060179035</v>
       </c>
       <c r="AF74" s="189" t="n">
         <v>1166.292607403642</v>
@@ -8001,7 +8001,7 @@
         <v>1538.128009867686</v>
       </c>
       <c r="AH74" s="190" t="n">
-        <v>1961.409950895412</v>
+        <v>1961.409950895411</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" thickBot="1"/>
@@ -8263,7 +8263,7 @@
         <v>371.1529690312057</v>
       </c>
       <c r="D79" s="149" t="n">
-        <v>418.5611273595749</v>
+        <v>418.561127359575</v>
       </c>
       <c r="E79" s="149" t="n">
         <v>462.0146715083237</v>
@@ -8293,7 +8293,7 @@
         <v>48310940.21805556</v>
       </c>
       <c r="N79" s="152" t="n">
-        <v>57802492.77026841</v>
+        <v>57802492.77026843</v>
       </c>
       <c r="O79" s="152" t="n">
         <v>67652106.21377982</v>
@@ -8313,7 +8313,7 @@
         <v>450.1376299910323</v>
       </c>
       <c r="U79" s="149" t="n">
-        <v>507.634667096446</v>
+        <v>507.6346670964461</v>
       </c>
       <c r="V79" s="149" t="n">
         <v>560.3355128660079</v>
@@ -8328,7 +8328,7 @@
         <v>48.32394607295165</v>
       </c>
       <c r="Z79" s="149" t="n">
-        <v>56.89489379071415</v>
+        <v>56.89489379071417</v>
       </c>
       <c r="AA79" s="149" t="n">
         <v>65.63341322971775</v>
@@ -8343,7 +8343,7 @@
         <v>48310940.21805556</v>
       </c>
       <c r="AE79" s="152" t="n">
-        <v>57802492.77026841</v>
+        <v>57802492.77026843</v>
       </c>
       <c r="AF79" s="152" t="n">
         <v>67652106.21377982</v>
@@ -8365,7 +8365,7 @@
         <v>867.9877729507367</v>
       </c>
       <c r="D80" s="156" t="n">
-        <v>985.9754286659363</v>
+        <v>985.9754286659361</v>
       </c>
       <c r="E80" s="156" t="n">
         <v>1087.915561349591</v>
@@ -8380,13 +8380,13 @@
         <v>61.05896759574955</v>
       </c>
       <c r="I80" s="156" t="n">
-        <v>70.41146453472788</v>
+        <v>70.41146453472787</v>
       </c>
       <c r="J80" s="156" t="n">
-        <v>80.56038005687931</v>
+        <v>80.56038005687934</v>
       </c>
       <c r="K80" s="156" t="n">
-        <v>91.43219507255513</v>
+        <v>91.43219507255516</v>
       </c>
       <c r="L80" s="157" t="n">
         <v>104.2198748072343</v>
@@ -8398,10 +8398,10 @@
         <v>19176887.39222207</v>
       </c>
       <c r="O80" s="159" t="n">
-        <v>22091889.72478593</v>
+        <v>22091889.72478594</v>
       </c>
       <c r="P80" s="159" t="n">
-        <v>25225811.7438581</v>
+        <v>25225811.74385811</v>
       </c>
       <c r="Q80" s="160" t="n">
         <v>28996773.71504542</v>
@@ -8430,13 +8430,13 @@
         <v>61.31521118739611</v>
       </c>
       <c r="Z80" s="156" t="n">
-        <v>70.70776734606902</v>
+        <v>70.70776734606901</v>
       </c>
       <c r="AA80" s="156" t="n">
-        <v>80.90168054015381</v>
+        <v>80.90168054015383</v>
       </c>
       <c r="AB80" s="156" t="n">
-        <v>91.82417409771725</v>
+        <v>91.82417409771728</v>
       </c>
       <c r="AC80" s="157" t="n">
         <v>104.6731564520402</v>
@@ -8448,10 +8448,10 @@
         <v>19176887.39222207</v>
       </c>
       <c r="AF80" s="159" t="n">
-        <v>22091889.72478593</v>
+        <v>22091889.72478594</v>
       </c>
       <c r="AG80" s="159" t="n">
-        <v>25225811.7438581</v>
+        <v>25225811.74385811</v>
       </c>
       <c r="AH80" s="160" t="n">
         <v>28996773.71504542</v>
@@ -8470,7 +8470,7 @@
         <v>488.6098295515984</v>
       </c>
       <c r="E81" s="162" t="n">
-        <v>538.2429667532142</v>
+        <v>538.2429667532143</v>
       </c>
       <c r="F81" s="162" t="n">
         <v>582.1228220375576</v>
@@ -8485,7 +8485,7 @@
         <v>50.32274904231752</v>
       </c>
       <c r="J81" s="162" t="n">
-        <v>57.90818163820619</v>
+        <v>57.9081816382062</v>
       </c>
       <c r="K81" s="162" t="n">
         <v>66.14366423861226</v>
@@ -8500,7 +8500,7 @@
         <v>76979380.16249049</v>
       </c>
       <c r="O81" s="165" t="n">
-        <v>89743995.93856575</v>
+        <v>89743995.93856576</v>
       </c>
       <c r="P81" s="165" t="n">
         <v>103744735.3259007</v>
@@ -8520,10 +8520,10 @@
         <v>578.6118256417923</v>
       </c>
       <c r="V81" s="162" t="n">
-        <v>637.5899644815802</v>
+        <v>637.5899644815803</v>
       </c>
       <c r="W81" s="162" t="n">
-        <v>689.555359938567</v>
+        <v>689.5553599385671</v>
       </c>
       <c r="X81" s="163" t="n">
         <v>743.5508022712662</v>
@@ -8535,10 +8535,10 @@
         <v>59.80534709262682</v>
       </c>
       <c r="AA81" s="162" t="n">
-        <v>68.83116536728511</v>
+        <v>68.83116536728512</v>
       </c>
       <c r="AB81" s="162" t="n">
-        <v>78.63029360832901</v>
+        <v>78.63029360832903</v>
       </c>
       <c r="AC81" s="163" t="n">
         <v>90.1832816873432</v>
@@ -8550,7 +8550,7 @@
         <v>76979380.16249049</v>
       </c>
       <c r="AF81" s="165" t="n">
-        <v>89743995.93856575</v>
+        <v>89743995.93856576</v>
       </c>
       <c r="AG81" s="165" t="n">
         <v>103744735.3259007</v>
@@ -8566,7 +8566,7 @@
         </is>
       </c>
       <c r="C82" s="155" t="n">
-        <v>887.4026902511041</v>
+        <v>887.4026902511038</v>
       </c>
       <c r="D82" s="156" t="n">
         <v>994.262092583524</v>
@@ -8581,7 +8581,7 @@
         <v>1262.007656740142</v>
       </c>
       <c r="H82" s="155" t="n">
-        <v>92.91734515866486</v>
+        <v>92.91734515866483</v>
       </c>
       <c r="I82" s="156" t="n">
         <v>107.3157336693798</v>
@@ -8596,7 +8596,7 @@
         <v>157.5811190013625</v>
       </c>
       <c r="M82" s="158" t="n">
-        <v>5950981.402304019</v>
+        <v>5950981.402304017</v>
       </c>
       <c r="N82" s="159" t="n">
         <v>6964942.105541305</v>
@@ -8616,7 +8616,7 @@
         </is>
       </c>
       <c r="T82" s="155" t="n">
-        <v>1147.149601152195</v>
+        <v>1147.149601152194</v>
       </c>
       <c r="U82" s="156" t="n">
         <v>1285.287249495711</v>
@@ -8631,7 +8631,7 @@
         <v>1631.403190439751</v>
       </c>
       <c r="Y82" s="155" t="n">
-        <v>106.6159499875865</v>
+        <v>106.6159499875864</v>
       </c>
       <c r="Z82" s="156" t="n">
         <v>123.1869765198199</v>
@@ -8646,7 +8646,7 @@
         <v>181.2716523712877</v>
       </c>
       <c r="AD82" s="158" t="n">
-        <v>5950981.402304019</v>
+        <v>5950981.402304017</v>
       </c>
       <c r="AE82" s="159" t="n">
         <v>6964942.105541305</v>
@@ -8668,10 +8668,10 @@
         </is>
       </c>
       <c r="C83" s="161" t="n">
-        <v>453.9807114932033</v>
+        <v>453.9807114932032</v>
       </c>
       <c r="D83" s="162" t="n">
-        <v>510.1358165442354</v>
+        <v>510.1358165442356</v>
       </c>
       <c r="E83" s="162" t="n">
         <v>561.4807506472156</v>
@@ -8686,13 +8686,13 @@
         <v>45.02439893842167</v>
       </c>
       <c r="I83" s="162" t="n">
-        <v>52.64238449859977</v>
+        <v>52.64238449859978</v>
       </c>
       <c r="J83" s="162" t="n">
-        <v>60.51016115629136</v>
+        <v>60.51016115629137</v>
       </c>
       <c r="K83" s="162" t="n">
-        <v>69.08663081332156</v>
+        <v>69.08663081332158</v>
       </c>
       <c r="L83" s="163" t="n">
         <v>79.17700851183939</v>
@@ -8701,13 +8701,13 @@
         <v>70771595.62042493</v>
       </c>
       <c r="N83" s="165" t="n">
-        <v>83944322.26803178</v>
+        <v>83944322.26803179</v>
       </c>
       <c r="O83" s="165" t="n">
-        <v>97753600.69005334</v>
+        <v>97753600.69005336</v>
       </c>
       <c r="P83" s="165" t="n">
-        <v>112956912.4880533</v>
+        <v>112956912.4880534</v>
       </c>
       <c r="Q83" s="166" t="n">
         <v>131410284.9693355</v>
@@ -8718,46 +8718,46 @@
         </is>
       </c>
       <c r="T83" s="161" t="n">
-        <v>539.1520289626803</v>
+        <v>539.1520289626802</v>
       </c>
       <c r="U83" s="162" t="n">
-        <v>606.2692353587754</v>
+        <v>606.2692353587755</v>
       </c>
       <c r="V83" s="162" t="n">
-        <v>667.478598272744</v>
+        <v>667.4785982727441</v>
       </c>
       <c r="W83" s="162" t="n">
-        <v>721.6380006678518</v>
+        <v>721.6380006678519</v>
       </c>
       <c r="X83" s="163" t="n">
         <v>777.8281437112111</v>
       </c>
       <c r="Y83" s="161" t="n">
-        <v>53.42031120819428</v>
+        <v>53.42031120819426</v>
       </c>
       <c r="Z83" s="162" t="n">
-        <v>62.47228034398188</v>
+        <v>62.47228034398189</v>
       </c>
       <c r="AA83" s="162" t="n">
-        <v>71.82181746724268</v>
+        <v>71.8218174672427</v>
       </c>
       <c r="AB83" s="162" t="n">
-        <v>82.01436904689704</v>
+        <v>82.01436904689707</v>
       </c>
       <c r="AC83" s="163" t="n">
-        <v>94.00838940980245</v>
+        <v>94.00838940980246</v>
       </c>
       <c r="AD83" s="164" t="n">
         <v>70771595.62042493</v>
       </c>
       <c r="AE83" s="165" t="n">
-        <v>83944322.26803178</v>
+        <v>83944322.26803179</v>
       </c>
       <c r="AF83" s="165" t="n">
-        <v>97753600.69005334</v>
+        <v>97753600.69005336</v>
       </c>
       <c r="AG83" s="165" t="n">
-        <v>112956912.4880533</v>
+        <v>112956912.4880534</v>
       </c>
       <c r="AH83" s="166" t="n">
         <v>131410284.9693355</v>
@@ -8770,7 +8770,7 @@
         </is>
       </c>
       <c r="C84" s="155" t="n">
-        <v>9856.509602128159</v>
+        <v>9856.509602128157</v>
       </c>
       <c r="D84" s="156" t="n">
         <v>10573.18358349628</v>
@@ -8782,10 +8782,10 @@
         <v>12007.20544274847</v>
       </c>
       <c r="G84" s="157" t="n">
-        <v>12795.83540307118</v>
+        <v>12795.83540307119</v>
       </c>
       <c r="H84" s="155" t="n">
-        <v>9727.166810655615</v>
+        <v>9727.166810655614</v>
       </c>
       <c r="I84" s="156" t="n">
         <v>10203.21415503257</v>
@@ -8800,7 +8800,7 @@
         <v>12275.4812549597</v>
       </c>
       <c r="M84" s="158" t="n">
-        <v>64478939.66509265</v>
+        <v>64478939.66509264</v>
       </c>
       <c r="N84" s="159" t="n">
         <v>73221789.89096428</v>
@@ -8820,7 +8820,7 @@
         </is>
       </c>
       <c r="T84" s="155" t="n">
-        <v>5534.690212522152</v>
+        <v>5534.69021252215</v>
       </c>
       <c r="U84" s="156" t="n">
         <v>5937.121563006606</v>
@@ -8832,10 +8832,10 @@
         <v>6742.362674650451</v>
       </c>
       <c r="X84" s="157" t="n">
-        <v>7185.199205926941</v>
+        <v>7185.199205926943</v>
       </c>
       <c r="Y84" s="155" t="n">
-        <v>5493.670872230832</v>
+        <v>5493.67087223083</v>
       </c>
       <c r="Z84" s="156" t="n">
         <v>5818.648096165955</v>
@@ -8847,10 +8847,10 @@
         <v>6574.986840522045</v>
       </c>
       <c r="AC84" s="157" t="n">
-        <v>7018.146659054908</v>
+        <v>7018.14665905491</v>
       </c>
       <c r="AD84" s="158" t="n">
-        <v>64478939.66509265</v>
+        <v>64478939.66509264</v>
       </c>
       <c r="AE84" s="159" t="n">
         <v>73221789.89096428</v>
@@ -8872,28 +8872,28 @@
         </is>
       </c>
       <c r="C85" s="179" t="n">
-        <v>832.6545167388356</v>
+        <v>832.6545167388354</v>
       </c>
       <c r="D85" s="180" t="n">
         <v>916.5373865246629</v>
       </c>
       <c r="E85" s="180" t="n">
-        <v>1002.150286957989</v>
+        <v>1002.15028695799</v>
       </c>
       <c r="F85" s="180" t="n">
-        <v>1083.297692359728</v>
+        <v>1083.297692359729</v>
       </c>
       <c r="G85" s="181" t="n">
-        <v>1168.683081810337</v>
+        <v>1168.683081810338</v>
       </c>
       <c r="H85" s="179" t="n">
         <v>85.68410982590433</v>
       </c>
       <c r="I85" s="180" t="n">
-        <v>98.1189829227504</v>
+        <v>98.11898292275042</v>
       </c>
       <c r="J85" s="180" t="n">
-        <v>112.0855544259143</v>
+        <v>112.0855544259144</v>
       </c>
       <c r="K85" s="180" t="n">
         <v>127.9969249683037</v>
@@ -8908,13 +8908,13 @@
         <v>157166112.1589961</v>
       </c>
       <c r="O85" s="183" t="n">
-        <v>181948399.5364722</v>
+        <v>181948399.5364723</v>
       </c>
       <c r="P85" s="183" t="n">
-        <v>210360873.6846774</v>
+        <v>210360873.6846775</v>
       </c>
       <c r="Q85" s="184" t="n">
-        <v>245073991.7913114</v>
+        <v>245073991.7913115</v>
       </c>
       <c r="S85" s="51" t="inlineStr">
         <is>
@@ -8922,13 +8922,13 @@
         </is>
       </c>
       <c r="T85" s="185" t="n">
-        <v>946.3731084958531</v>
+        <v>946.373108495853</v>
       </c>
       <c r="U85" s="186" t="n">
         <v>1042.261591971441</v>
       </c>
       <c r="V85" s="186" t="n">
-        <v>1139.068942912699</v>
+        <v>1139.0689429127</v>
       </c>
       <c r="W85" s="186" t="n">
         <v>1230.359991072456</v>
@@ -8958,13 +8958,13 @@
         <v>157166112.1589961</v>
       </c>
       <c r="AF85" s="189" t="n">
-        <v>181948399.5364722</v>
+        <v>181948399.5364723</v>
       </c>
       <c r="AG85" s="189" t="n">
-        <v>210360873.6846774</v>
+        <v>210360873.6846775</v>
       </c>
       <c r="AH85" s="190" t="n">
-        <v>245073991.7913114</v>
+        <v>245073991.7913115</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" thickBot="1"/>
@@ -9756,7 +9756,7 @@
         </is>
       </c>
       <c r="C94" s="85" t="n">
-        <v>155891.194997355</v>
+        <v>155891.1949973551</v>
       </c>
       <c r="D94" s="86" t="n">
         <v>164552.8887516423</v>
@@ -9836,7 +9836,7 @@
         <v>1228911.857167671</v>
       </c>
       <c r="AD94" s="85" t="n">
-        <v>1324806.876257379</v>
+        <v>1324806.87625738</v>
       </c>
       <c r="AE94" s="86" t="n">
         <v>1343705.108983081</v>
@@ -9988,7 +9988,7 @@
         </is>
       </c>
       <c r="C96" s="132" t="n">
-        <v>162432.9569666398</v>
+        <v>162432.9569666399</v>
       </c>
       <c r="D96" s="133" t="n">
         <v>171478.1245912296</v>
